--- a/data_RS.xlsx
+++ b/data_RS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mathe\Área de Trabalho\ProjetoLogistica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A008C9E-E856-4FBE-B4E0-C96EC795D8B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7316AF7E-92D8-41D9-A6A4-546ACD46D7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data_RS.xlsx
+++ b/data_RS.xlsx
@@ -4,37 +4,31 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="8"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="(URF) 1010252 - JAGUARAO_Acordo"/>
-    <sheet r:id="rId2" sheetId="2" name="(URF) 1010252 - JAGUARAO_Agrone"/>
-    <sheet r:id="rId3" sheetId="3" name="(URF) 1010253 - BAGE_Acordo Agr"/>
-    <sheet r:id="rId4" sheetId="4" name="(URF) 1010253 - BAGE_Agronegóci"/>
-    <sheet r:id="rId5" sheetId="5" name="(URF) 1010351 - IRF SANTANA DO "/>
-    <sheet r:id="rId6" sheetId="6" name="(URF) 1010900 - URUGUAIANA_Acor"/>
-    <sheet r:id="rId7" sheetId="7" name="(URF) 1010900 - URUGUAIANA_Agro"/>
-    <sheet r:id="rId8" sheetId="8" name="(URF) 1010953 - SAO BORJA_Acord"/>
-    <sheet r:id="rId9" sheetId="9" name="(URF) 1010953 - SAO BORJA_Agron"/>
-    <sheet r:id="rId10" sheetId="10" name="(URF) 1015500 - CHUI_Acordo Agr"/>
-    <sheet r:id="rId11" sheetId="11" name="(URF) 1015500 - CHUI_Agronegóci"/>
-    <sheet r:id="rId12" sheetId="12" name="(URF) 1015600 - SANTANA DO LIVR"/>
-    <sheet r:id="rId13" sheetId="13" name="(URF) 1017500 - ALF - URUGUAIAN"/>
-    <sheet r:id="rId14" sheetId="14" name="(URF) 1017503 - IRF - SÃO BORJA"/>
-    <sheet r:id="rId15" sheetId="15" name="(URF) 1017600 - AEROPORTO SALGA"/>
-    <sheet r:id="rId16" sheetId="16" name="(URF) 1017700 - PORTO DE RIO GR"/>
-    <sheet r:id="rId17" sheetId="17" name="(URF) 1017701 - IRF - CHUÍ_Acor"/>
-    <sheet r:id="rId18" sheetId="18" name="(URF) 1017701 - IRF - CHUÍ_Agro"/>
-    <sheet r:id="rId19" sheetId="19" name="(URF) 1017800 - ALF - PORTO ALE"/>
-    <sheet r:id="rId20" sheetId="20" name="(URF) 1017801 - IRF - AEROPORTO"/>
-    <sheet r:id="rId21" sheetId="21" name="(URF) 1017900 - ALF - SANTANA D"/>
+    <sheet r:id="rId1" sheetId="1" name="(URF) 1010252 - JAGUARAO"/>
+    <sheet r:id="rId2" sheetId="2" name="(URF) 1010253 - BAGE"/>
+    <sheet r:id="rId3" sheetId="3" name="(URF) 1010351 - IRF SANTANA DO "/>
+    <sheet r:id="rId4" sheetId="4" name="(URF) 1010900 - URUGUAIANA"/>
+    <sheet r:id="rId5" sheetId="5" name="(URF) 1010953 - SAO BORJA"/>
+    <sheet r:id="rId6" sheetId="6" name="(URF) 1015500 - CHUI"/>
+    <sheet r:id="rId7" sheetId="7" name="(URF) 1015600 - SANTANA DO LIVR"/>
+    <sheet r:id="rId8" sheetId="8" name="(URF) 1017500 - ALF - URUGUAIAN"/>
+    <sheet r:id="rId9" sheetId="9" name="(URF) 1017503 - IRF - SÃO BORJA"/>
+    <sheet r:id="rId10" sheetId="10" name="(URF) 1017600 - AEROPORTO SALGA"/>
+    <sheet r:id="rId11" sheetId="11" name="(URF) 1017701 - IRF - CHUÍ"/>
+    <sheet r:id="rId12" sheetId="12" name="(URF) 1017700 - PORTO DE RIO GR"/>
+    <sheet r:id="rId13" sheetId="13" name="(URF) 1017800 - ALF - PORTO ALE"/>
+    <sheet r:id="rId14" sheetId="14" name="(URF) 1017801 - IRF - AEROPORTO"/>
+    <sheet r:id="rId15" sheetId="15" name="(URF) 1017900 - ALF - SANTANA D"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="45">
   <si>
     <t>Agrupamento</t>
   </si>
@@ -96,19 +90,19 @@
     <t>1017800 - ALF - PORTO ALEGRE</t>
   </si>
   <si>
-    <t>(URF) 1017701 - IRF - CHUÍ</t>
+    <t>(URF) 1017700 - PORTO DE RIO GRANDE</t>
   </si>
   <si>
-    <t>1017701 - IRF - CHUÍ</t>
+    <t>1017700 - PORTO DE RIO GRANDE</t>
   </si>
   <si>
     <t>Acordo Agrícola OMC e Pescados</t>
   </si>
   <si>
-    <t>(URF) 1017700 - PORTO DE RIO GRANDE</t>
+    <t>(URF) 1017701 - IRF - CHUÍ</t>
   </si>
   <si>
-    <t>1017700 - PORTO DE RIO GRANDE</t>
+    <t>1017701 - IRF - CHUÍ</t>
   </si>
   <si>
     <t>(URF) 1017600 - AEROPORTO SALGADO FILHO - PORTO ALEGRE</t>
@@ -176,7 +170,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,12 +181,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -246,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -260,23 +248,26 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,18 +571,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -939,6 +930,325 @@
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2015</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="4">
+        <v>4668048</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1279070</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2016</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="4">
+        <v>6078231</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1911530</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2017</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="4">
+        <v>12148063</v>
+      </c>
+      <c r="G15" s="4">
+        <v>3401707</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2018</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="4">
+        <v>31079162</v>
+      </c>
+      <c r="G16" s="4">
+        <v>8758699</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="4">
+        <v>44061849</v>
+      </c>
+      <c r="G17" s="4">
+        <v>12493424</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="4">
+        <v>43950611</v>
+      </c>
+      <c r="G18" s="4">
+        <v>12948287</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="4">
+        <v>45616208</v>
+      </c>
+      <c r="G19" s="4">
+        <v>11637209</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="4">
+        <v>34066303</v>
+      </c>
+      <c r="G20" s="4">
+        <v>7608748</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="4">
+        <v>33221686</v>
+      </c>
+      <c r="G21" s="4">
+        <v>8389688</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="4">
+        <v>34714828</v>
+      </c>
+      <c r="G22" s="4">
+        <v>8230802</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2025</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="4">
+        <v>42605588</v>
+      </c>
+      <c r="G23" s="4">
+        <v>8131544</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -952,18 +1262,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -997,7 +1307,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -1009,24 +1319,24 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F2" s="4">
-        <v>36398741</v>
+        <v>239150</v>
       </c>
       <c r="G2" s="4">
-        <v>16202517</v>
+        <v>14141</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -1038,24 +1348,24 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46755925</v>
+        <v>25</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="4">
-        <v>22658563</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -1067,24 +1377,24 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="4">
-        <v>56448283</v>
+        <v>25</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G4" s="4">
-        <v>22945275</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
@@ -1096,7 +1406,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>13</v>
@@ -1108,12 +1418,12 @@
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -1125,7 +1435,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -1137,12 +1447,12 @@
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
@@ -1154,7 +1464,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>13</v>
@@ -1166,12 +1476,12 @@
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
@@ -1183,7 +1493,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>13</v>
@@ -1195,12 +1505,12 @@
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
@@ -1212,7 +1522,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>13</v>
@@ -1224,12 +1534,12 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -1241,7 +1551,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>13</v>
@@ -1253,12 +1563,12 @@
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
@@ -1270,7 +1580,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>13</v>
@@ -1282,12 +1592,12 @@
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>10</v>
@@ -1299,7 +1609,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>13</v>
@@ -1311,8 +1621,19 @@
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>34</v>
-      </c>
+        <v>26</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1324,18 +1645,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1369,7 +1690,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -1381,24 +1702,24 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="4">
-        <v>36398741</v>
+        <v>23</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G2" s="4">
-        <v>16202517</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -1410,24 +1731,24 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46755925</v>
+        <v>23</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="4">
-        <v>22658563</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -1439,24 +1760,24 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="4">
-        <v>56448283</v>
+        <v>23</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G4" s="4">
-        <v>22945275</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
@@ -1468,24 +1789,24 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F5" s="4">
+        <v>65346637</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>31293407</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -1497,24 +1818,24 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F6" s="4">
+        <v>107878137</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>41483484</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
@@ -1526,24 +1847,24 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F7" s="4">
+        <v>116693634</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>42471461</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
@@ -1555,24 +1876,24 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F8" s="4">
+        <v>125730834</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>42895255</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
@@ -1584,24 +1905,24 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F9" s="4">
+        <v>158222716</v>
       </c>
       <c r="G9" s="4">
-        <v>0</v>
+        <v>51310637</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -1613,24 +1934,24 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F10" s="4">
+        <v>173777248</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>57354844</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
@@ -1642,24 +1963,24 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F11" s="4">
+        <v>187367985</v>
       </c>
       <c r="G11" s="4">
-        <v>0</v>
+        <v>58064792</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>10</v>
@@ -1671,19 +1992,19 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="F12" s="4">
+        <v>262317068</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>70240574</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -1694,25 +2015,315 @@
         <v>10</v>
       </c>
       <c r="C13" s="4">
+        <v>2015</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2016</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2017</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2018</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="4">
+        <v>65346637</v>
+      </c>
+      <c r="G16" s="4">
+        <v>31293407</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="4">
+        <v>107878137</v>
+      </c>
+      <c r="G17" s="4">
+        <v>41483484</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="4">
+        <v>116693634</v>
+      </c>
+      <c r="G18" s="4">
+        <v>42471461</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="4">
+        <v>125730834</v>
+      </c>
+      <c r="G19" s="4">
+        <v>42895255</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="4">
+        <v>158222716</v>
+      </c>
+      <c r="G20" s="4">
+        <v>51310637</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="4">
+        <v>173777248</v>
+      </c>
+      <c r="G21" s="4">
+        <v>57354844</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="4">
+        <v>187367985</v>
+      </c>
+      <c r="G22" s="4">
+        <v>58064792</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4">
         <v>2025</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>34</v>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="4">
+        <v>262317068</v>
+      </c>
+      <c r="G23" s="4">
+        <v>70240574</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1728,15 +2339,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -1782,19 +2393,19 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F2" s="4">
-        <v>25495585</v>
+        <v>954855773</v>
       </c>
       <c r="G2" s="4">
-        <v>9661444</v>
+        <v>485784020</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -1811,19 +2422,19 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4">
-        <v>24036927</v>
+        <v>812252683</v>
       </c>
       <c r="G3" s="4">
-        <v>10331830</v>
+        <v>442010608</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -1840,19 +2451,19 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4">
-        <v>29065264</v>
+        <v>822709279</v>
       </c>
       <c r="G4" s="4">
-        <v>10719293</v>
+        <v>409190491</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -1869,19 +2480,19 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="F5" s="4">
+        <v>840885987</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>442083878</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -1898,19 +2509,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1012198441</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>486725696</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -1927,19 +2538,19 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1136343434</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>531338603</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -1956,19 +2567,19 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1063427179</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>482999234</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -1985,19 +2596,19 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1122084936</v>
       </c>
       <c r="G9" s="4">
-        <v>0</v>
+        <v>480680521</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -2014,19 +2625,19 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1273713767</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>571383157</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -2043,19 +2654,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1276345725</v>
       </c>
       <c r="G11" s="4">
-        <v>0</v>
+        <v>575897435</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -2072,49 +2683,31 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1120114746</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>454125456</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2129,15 +2722,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -2183,9 +2776,9 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G2" s="4">
@@ -2195,7 +2788,7 @@
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -2212,9 +2805,9 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="4">
@@ -2224,7 +2817,7 @@
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -2241,9 +2834,9 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G4" s="4">
@@ -2253,7 +2846,7 @@
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -2270,19 +2863,19 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F5" s="4">
-        <v>29454534</v>
+        <v>15871</v>
       </c>
       <c r="G5" s="4">
-        <v>12506101</v>
+        <v>4162</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -2299,19 +2892,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F6" s="4">
-        <v>25694256</v>
+        <v>80013</v>
       </c>
       <c r="G6" s="4">
-        <v>10273352</v>
+        <v>19094</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -2328,19 +2921,19 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F7" s="4">
-        <v>16153848</v>
+        <v>89009</v>
       </c>
       <c r="G7" s="4">
-        <v>7366643</v>
+        <v>20805</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -2357,19 +2950,19 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F8" s="4">
-        <v>31335623</v>
+        <v>63515</v>
       </c>
       <c r="G8" s="4">
-        <v>11085612</v>
+        <v>13752</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -2386,19 +2979,19 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F9" s="4">
-        <v>16675419</v>
+        <v>84988</v>
       </c>
       <c r="G9" s="4">
-        <v>6452607</v>
+        <v>13952</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -2415,19 +3008,19 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F10" s="4">
-        <v>10469797</v>
+        <v>117276</v>
       </c>
       <c r="G10" s="4">
-        <v>3799676</v>
+        <v>21599</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -2444,19 +3037,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F11" s="4">
-        <v>15853148</v>
+        <v>101051</v>
       </c>
       <c r="G11" s="4">
-        <v>5993537</v>
+        <v>19162</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -2473,49 +3066,31 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F12" s="4">
-        <v>32027258</v>
+        <v>128546</v>
       </c>
       <c r="G12" s="4">
-        <v>10809595</v>
+        <v>19740</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="4">
-        <v>32027258</v>
-      </c>
-      <c r="G13" s="4">
-        <v>10809595</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2530,15 +3105,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -2584,9 +3159,9 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G2" s="4">
@@ -2596,7 +3171,7 @@
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -2613,9 +3188,9 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="4">
@@ -2625,7 +3200,7 @@
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -2642,9 +3217,9 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G4" s="4">
@@ -2654,7 +3229,7 @@
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -2671,19 +3246,19 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="4">
-        <v>324202743</v>
+        <v>16</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G5" s="4">
-        <v>128612210</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -2700,19 +3275,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F6" s="4">
-        <v>406524579</v>
+        <v>16688</v>
       </c>
       <c r="G6" s="4">
-        <v>147504720</v>
+        <v>987</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -2729,19 +3304,19 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F7" s="4">
-        <v>411837802</v>
+        <v>10265</v>
       </c>
       <c r="G7" s="4">
-        <v>144924295</v>
+        <v>622</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -2758,19 +3333,19 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="4">
-        <v>654459936</v>
+        <v>16</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G8" s="4">
-        <v>216055261</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -2787,19 +3362,19 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F9" s="4">
-        <v>696051137</v>
+        <v>30</v>
       </c>
       <c r="G9" s="4">
-        <v>227900588</v>
+        <v>30</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -2816,19 +3391,19 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F10" s="4">
-        <v>692086017</v>
+        <v>909</v>
       </c>
       <c r="G10" s="4">
-        <v>235108168</v>
+        <v>168</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -2845,19 +3420,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F11" s="4">
-        <v>810613918</v>
+        <v>631</v>
       </c>
       <c r="G11" s="4">
-        <v>270508386</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -2874,49 +3449,31 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1241438021</v>
+        <v>16</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G12" s="4">
-        <v>366178646</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="4">
-        <v>1241438021</v>
-      </c>
-      <c r="G13" s="4">
-        <v>366178646</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2928,18 +3485,20 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -2970,6 +3529,8 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
@@ -2985,20 +3546,22 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="4">
-        <v>239150</v>
+        <v>12</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G2" s="4">
-        <v>14141</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
@@ -3014,7 +3577,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>13</v>
@@ -3026,8 +3589,10 @@
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
@@ -3043,7 +3608,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>13</v>
@@ -3055,8 +3620,10 @@
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="6"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
@@ -3072,20 +3639,22 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F5" s="4">
+        <v>28727514</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>12297084</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
@@ -3101,20 +3670,22 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F6" s="4">
+        <v>48829672</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>18859377</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
@@ -3130,7 +3701,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>13</v>
@@ -3142,8 +3713,10 @@
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
@@ -3159,7 +3732,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>13</v>
@@ -3171,8 +3744,10 @@
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
@@ -3188,7 +3763,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>13</v>
@@ -3200,8 +3775,10 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
@@ -3217,7 +3794,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>13</v>
@@ -3229,8 +3806,10 @@
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
@@ -3246,7 +3825,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>13</v>
@@ -3258,8 +3837,10 @@
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
@@ -3275,7 +3856,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>13</v>
@@ -3287,1612 +3868,23 @@
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>26</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-  </cols>
-  <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2015</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="4">
-        <v>954855773</v>
-      </c>
-      <c r="G2" s="4">
-        <v>485784020</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2016</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="4">
-        <v>812252683</v>
-      </c>
-      <c r="G3" s="4">
-        <v>442010608</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2017</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="4">
-        <v>822709279</v>
-      </c>
-      <c r="G4" s="4">
-        <v>409190491</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2018</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="4">
-        <v>840885987</v>
-      </c>
-      <c r="G5" s="4">
-        <v>442083878</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2019</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="4">
-        <v>1012198441</v>
-      </c>
-      <c r="G6" s="4">
-        <v>486725696</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2020</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1136343434</v>
-      </c>
-      <c r="G7" s="4">
-        <v>531338603</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2021</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="4">
-        <v>1063427179</v>
-      </c>
-      <c r="G8" s="4">
-        <v>482999234</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2022</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1122084936</v>
-      </c>
-      <c r="G9" s="4">
-        <v>480680521</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2023</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1273713767</v>
-      </c>
-      <c r="G10" s="4">
-        <v>571383157</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2024</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1276345725</v>
-      </c>
-      <c r="G11" s="4">
-        <v>575897435</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1120114746</v>
-      </c>
-      <c r="G12" s="4">
-        <v>454125456</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="4">
-        <v>1120114746</v>
-      </c>
-      <c r="G13" s="4">
-        <v>454125456</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-  </cols>
-  <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2015</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2016</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2017</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2018</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4">
-        <v>65346637</v>
-      </c>
-      <c r="G5" s="4">
-        <v>31293407</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2019</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4">
-        <v>107878137</v>
-      </c>
-      <c r="G6" s="4">
-        <v>41483484</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2020</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="4">
-        <v>116693634</v>
-      </c>
-      <c r="G7" s="4">
-        <v>42471461</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2021</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="4">
-        <v>125730834</v>
-      </c>
-      <c r="G8" s="4">
-        <v>42895255</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2022</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="4">
-        <v>158222716</v>
-      </c>
-      <c r="G9" s="4">
-        <v>51310637</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2023</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="4">
-        <v>173777248</v>
-      </c>
-      <c r="G10" s="4">
-        <v>57354844</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2024</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="4">
-        <v>187367985</v>
-      </c>
-      <c r="G11" s="4">
-        <v>58064792</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="4">
-        <v>262317068</v>
-      </c>
-      <c r="G12" s="4">
-        <v>70240574</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-  </cols>
-  <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2015</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2016</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2017</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2018</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4">
-        <v>65346637</v>
-      </c>
-      <c r="G5" s="4">
-        <v>31293407</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2019</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4">
-        <v>107878137</v>
-      </c>
-      <c r="G6" s="4">
-        <v>41483484</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2020</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="4">
-        <v>116693634</v>
-      </c>
-      <c r="G7" s="4">
-        <v>42471461</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2021</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="4">
-        <v>125730834</v>
-      </c>
-      <c r="G8" s="4">
-        <v>42895255</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2022</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="4">
-        <v>158222716</v>
-      </c>
-      <c r="G9" s="4">
-        <v>51310637</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2023</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="4">
-        <v>173777248</v>
-      </c>
-      <c r="G10" s="4">
-        <v>57354844</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2024</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="4">
-        <v>187367985</v>
-      </c>
-      <c r="G11" s="4">
-        <v>58064792</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="4">
-        <v>262317068</v>
-      </c>
-      <c r="G12" s="4">
-        <v>70240574</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="4">
-        <v>262317068</v>
-      </c>
-      <c r="G13" s="4">
-        <v>70240574</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-  </cols>
-  <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2015</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2016</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2017</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2018</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="4">
-        <v>15871</v>
-      </c>
-      <c r="G5" s="4">
-        <v>4162</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2019</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="4">
-        <v>80013</v>
-      </c>
-      <c r="G6" s="4">
-        <v>19094</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2020</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="4">
-        <v>89009</v>
-      </c>
-      <c r="G7" s="4">
-        <v>20805</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2021</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="4">
-        <v>63515</v>
-      </c>
-      <c r="G8" s="4">
-        <v>13752</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2022</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="4">
-        <v>84988</v>
-      </c>
-      <c r="G9" s="4">
-        <v>13952</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2023</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="4">
-        <v>117276</v>
-      </c>
-      <c r="G10" s="4">
-        <v>21599</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2024</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="4">
-        <v>101051</v>
-      </c>
-      <c r="G11" s="4">
-        <v>19162</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="4">
-        <v>128546</v>
-      </c>
-      <c r="G12" s="4">
-        <v>19740</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="4">
-        <v>128546</v>
-      </c>
-      <c r="G13" s="4">
-        <v>19740</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4904,18 +3896,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -4949,7 +3941,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -4961,24 +3953,24 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F2" s="4">
-        <v>4668048</v>
+        <v>1261757</v>
       </c>
       <c r="G2" s="4">
-        <v>1279070</v>
+        <v>401432</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -4990,24 +3982,24 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F3" s="4">
-        <v>6078231</v>
+        <v>36017</v>
       </c>
       <c r="G3" s="4">
-        <v>1911530</v>
+        <v>20159</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -5019,24 +4011,24 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="4">
-        <v>12148063</v>
+        <v>41</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G4" s="4">
-        <v>3401707</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
@@ -5048,24 +4040,24 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="4">
-        <v>31079162</v>
+        <v>41</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G5" s="4">
-        <v>8758699</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -5077,24 +4069,24 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="4">
-        <v>44061849</v>
+        <v>41</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G6" s="4">
-        <v>12493424</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
@@ -5106,24 +4098,24 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="4">
-        <v>43950611</v>
+        <v>41</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G7" s="4">
-        <v>12948287</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
@@ -5135,24 +4127,24 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="4">
-        <v>45616208</v>
+        <v>41</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G8" s="4">
-        <v>11637209</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
@@ -5164,24 +4156,24 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="4">
-        <v>34066303</v>
+        <v>41</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G9" s="4">
-        <v>7608748</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -5193,24 +4185,24 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="4">
-        <v>33221686</v>
+        <v>41</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G10" s="4">
-        <v>8389688</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
@@ -5222,24 +4214,24 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="4">
-        <v>34714828</v>
+        <v>41</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G11" s="4">
-        <v>8230802</v>
+        <v>0</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>10</v>
@@ -5251,19 +4243,19 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="4">
-        <v>42605588</v>
+        <v>41</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G12" s="4">
-        <v>8131544</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -5274,856 +4266,316 @@
         <v>10</v>
       </c>
       <c r="C13" s="4">
+        <v>2015</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1261757</v>
+      </c>
+      <c r="G13" s="4">
+        <v>401432</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2016</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="4">
+        <v>36017</v>
+      </c>
+      <c r="G14" s="4">
+        <v>20159</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2017</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2018</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4">
         <v>2025</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" s="4">
-        <v>42605588</v>
-      </c>
-      <c r="G13" s="4">
-        <v>8131544</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-  </cols>
-  <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2015</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2016</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2017</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2018</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2019</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="4">
-        <v>16688</v>
-      </c>
-      <c r="G6" s="4">
-        <v>987</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2020</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="4">
-        <v>10265</v>
-      </c>
-      <c r="G7" s="4">
-        <v>622</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2021</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2022</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="4">
-        <v>30</v>
-      </c>
-      <c r="G9" s="4">
-        <v>30</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2023</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="4">
-        <v>909</v>
-      </c>
-      <c r="G10" s="4">
-        <v>168</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2024</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="4">
-        <v>631</v>
-      </c>
-      <c r="G11" s="4">
-        <v>96</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-  </cols>
-  <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="4">
-        <v>2015</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2016</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2017</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2018</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="4">
-        <v>28727514</v>
-      </c>
-      <c r="G5" s="4">
-        <v>12297084</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2019</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="4">
-        <v>48829672</v>
-      </c>
-      <c r="G6" s="4">
-        <v>18859377</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2020</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4">
-        <v>2021</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2022</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2023</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4">
-        <v>2024</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6135,18 +4587,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -6180,7 +4632,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -6192,24 +4644,24 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="4">
-        <v>1261757</v>
+        <v>39</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G2" s="4">
-        <v>401432</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -6221,24 +4673,24 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="4">
-        <v>36017</v>
+        <v>39</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="4">
-        <v>20159</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -6250,9 +4702,9 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G4" s="4">
@@ -6262,12 +4714,12 @@
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
@@ -6279,9 +4731,9 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="4">
@@ -6291,12 +4743,12 @@
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -6308,9 +4760,9 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="4">
@@ -6320,12 +4772,12 @@
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
@@ -6337,24 +4789,24 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
+        <v>39</v>
+      </c>
+      <c r="F7" s="4">
+        <v>36915961</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>14388422</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
@@ -6366,24 +4818,24 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>13</v>
+        <v>39</v>
+      </c>
+      <c r="F8" s="4">
+        <v>35916799</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>15401903</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
@@ -6395,24 +4847,24 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>13</v>
+        <v>39</v>
+      </c>
+      <c r="F9" s="4">
+        <v>37267853</v>
       </c>
       <c r="G9" s="4">
-        <v>0</v>
+        <v>17322993</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -6424,24 +4876,24 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>13</v>
+        <v>39</v>
+      </c>
+      <c r="F10" s="4">
+        <v>42305553</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>17684656</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
@@ -6453,24 +4905,24 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>13</v>
+        <v>39</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46627406</v>
       </c>
       <c r="G11" s="4">
-        <v>0</v>
+        <v>18690515</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>10</v>
@@ -6482,20 +4934,31 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>13</v>
+        <v>39</v>
+      </c>
+      <c r="F12" s="4">
+        <v>58893750</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>20686368</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>42</v>
-      </c>
+        <v>40</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6507,21 +4970,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6550,9 +5013,9 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -6564,24 +5027,24 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F2" s="4">
-        <v>1261757</v>
+        <v>33829835</v>
       </c>
       <c r="G2" s="4">
-        <v>401432</v>
+        <v>10472798</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -6593,24 +5056,24 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F3" s="4">
-        <v>36017</v>
+        <v>39483552</v>
       </c>
       <c r="G3" s="4">
-        <v>20159</v>
+        <v>16868274</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -6622,24 +5085,24 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>13</v>
+        <v>37</v>
+      </c>
+      <c r="F4" s="4">
+        <v>24419315</v>
       </c>
       <c r="G4" s="4">
-        <v>0</v>
+        <v>8534603</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
@@ -6651,7 +5114,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>13</v>
@@ -6663,12 +5126,12 @@
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -6680,7 +5143,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -6692,12 +5155,12 @@
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
@@ -6709,7 +5172,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>13</v>
@@ -6721,12 +5184,12 @@
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
@@ -6738,7 +5201,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>13</v>
@@ -6750,12 +5213,12 @@
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
@@ -6767,7 +5230,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>13</v>
@@ -6779,12 +5242,12 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -6796,7 +5259,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>13</v>
@@ -6808,12 +5271,12 @@
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
@@ -6825,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>13</v>
@@ -6837,12 +5300,12 @@
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>10</v>
@@ -6854,7 +5317,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>13</v>
@@ -6866,7 +5329,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -6877,25 +5340,315 @@
         <v>10</v>
       </c>
       <c r="C13" s="4">
+        <v>2015</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="4">
+        <v>33829835</v>
+      </c>
+      <c r="G13" s="4">
+        <v>10472798</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2016</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="4">
+        <v>39483552</v>
+      </c>
+      <c r="G14" s="4">
+        <v>16868274</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2017</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F15" s="4">
+        <v>24419315</v>
+      </c>
+      <c r="G15" s="4">
+        <v>8534603</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2018</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4">
         <v>2025</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>42</v>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -6908,18 +5661,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -6953,7 +5706,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -6965,24 +5718,24 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>13</v>
+        <v>35</v>
+      </c>
+      <c r="F2" s="4">
+        <v>101509937</v>
       </c>
       <c r="G2" s="4">
-        <v>0</v>
+        <v>29542529</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -6994,24 +5747,24 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>13</v>
+        <v>35</v>
+      </c>
+      <c r="F3" s="4">
+        <v>175795220</v>
       </c>
       <c r="G3" s="4">
-        <v>0</v>
+        <v>62513951</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -7023,24 +5776,24 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>13</v>
+        <v>35</v>
+      </c>
+      <c r="F4" s="4">
+        <v>266656979</v>
       </c>
       <c r="G4" s="4">
-        <v>0</v>
+        <v>92504061</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
@@ -7052,9 +5805,9 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G5" s="4">
@@ -7064,12 +5817,12 @@
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -7081,9 +5834,9 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="4">
@@ -7093,12 +5846,12 @@
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
@@ -7110,24 +5863,24 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="4">
-        <v>36915961</v>
+        <v>35</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G7" s="4">
-        <v>14388422</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
@@ -7139,24 +5892,24 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="4">
-        <v>35916799</v>
+        <v>35</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G8" s="4">
-        <v>15401903</v>
+        <v>0</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
@@ -7168,24 +5921,24 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4">
-        <v>37267853</v>
+        <v>35</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G9" s="4">
-        <v>17322993</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -7197,24 +5950,24 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="4">
-        <v>42305553</v>
+        <v>35</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G10" s="4">
-        <v>17684656</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
@@ -7226,24 +5979,24 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="4">
-        <v>46627406</v>
+        <v>35</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G11" s="4">
-        <v>18690515</v>
+        <v>0</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>10</v>
@@ -7255,19 +6008,19 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="4">
-        <v>58893750</v>
+        <v>35</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="G12" s="4">
-        <v>20686368</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -7278,25 +6031,315 @@
         <v>10</v>
       </c>
       <c r="C13" s="4">
+        <v>2015</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="4">
+        <v>101509937</v>
+      </c>
+      <c r="G13" s="4">
+        <v>29542529</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2016</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="4">
+        <v>175795220</v>
+      </c>
+      <c r="G14" s="4">
+        <v>62513951</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2017</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="4">
+        <v>266656979</v>
+      </c>
+      <c r="G15" s="4">
+        <v>92504061</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2018</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4">
         <v>2025</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="4">
-        <v>58893750</v>
-      </c>
-      <c r="G13" s="4">
-        <v>20686368</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>40</v>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -7309,18 +6352,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -7366,19 +6409,19 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F2" s="4">
-        <v>33829835</v>
+        <v>36398741</v>
       </c>
       <c r="G2" s="4">
-        <v>10472798</v>
+        <v>16202517</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -7395,19 +6438,19 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F3" s="4">
-        <v>39483552</v>
+        <v>46755925</v>
       </c>
       <c r="G3" s="4">
-        <v>16868274</v>
+        <v>22658563</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -7424,19 +6467,19 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F4" s="4">
-        <v>24419315</v>
+        <v>56448283</v>
       </c>
       <c r="G4" s="4">
-        <v>8534603</v>
+        <v>22945275</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -7453,7 +6496,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>13</v>
@@ -7465,7 +6508,7 @@
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -7482,7 +6525,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -7494,7 +6537,7 @@
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -7511,7 +6554,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>13</v>
@@ -7523,7 +6566,7 @@
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -7540,7 +6583,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>13</v>
@@ -7552,7 +6595,7 @@
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -7569,7 +6612,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>13</v>
@@ -7581,7 +6624,7 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -7598,7 +6641,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>13</v>
@@ -7610,7 +6653,7 @@
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -7627,7 +6670,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>13</v>
@@ -7639,7 +6682,7 @@
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -7656,7 +6699,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>13</v>
@@ -7668,7 +6711,326 @@
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2015</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="4">
+        <v>36398741</v>
+      </c>
+      <c r="G13" s="4">
+        <v>16202517</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2016</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46755925</v>
+      </c>
+      <c r="G14" s="4">
+        <v>22658563</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4">
+        <v>2017</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="4">
+        <v>56448283</v>
+      </c>
+      <c r="G15" s="4">
+        <v>22945275</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2018</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2019</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4">
+        <v>2022</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2023</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="4">
+        <v>2025</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -7684,15 +7046,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -7738,19 +7100,19 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F2" s="4">
-        <v>33829835</v>
+        <v>25495585</v>
       </c>
       <c r="G2" s="4">
-        <v>10472798</v>
+        <v>9661444</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -7767,19 +7129,19 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F3" s="4">
-        <v>39483552</v>
+        <v>24036927</v>
       </c>
       <c r="G3" s="4">
-        <v>16868274</v>
+        <v>10331830</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -7796,19 +7158,19 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4">
-        <v>24419315</v>
+        <v>29065264</v>
       </c>
       <c r="G4" s="4">
-        <v>8534603</v>
+        <v>10719293</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -7825,7 +7187,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>13</v>
@@ -7837,7 +7199,7 @@
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -7854,7 +7216,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>13</v>
@@ -7866,7 +7228,7 @@
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -7883,7 +7245,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>13</v>
@@ -7895,7 +7257,7 @@
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -7912,7 +7274,7 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>13</v>
@@ -7924,7 +7286,7 @@
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -7941,7 +7303,7 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>13</v>
@@ -7953,7 +7315,7 @@
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -7970,7 +7332,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>13</v>
@@ -7982,7 +7344,7 @@
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -7999,7 +7361,7 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>13</v>
@@ -8011,7 +7373,7 @@
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -8028,7 +7390,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>13</v>
@@ -8040,37 +7402,19 @@
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8082,18 +7426,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -8127,7 +7471,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -8139,24 +7483,24 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="4">
-        <v>101509937</v>
+        <v>29</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G2" s="4">
-        <v>29542529</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
@@ -8168,24 +7512,24 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="4">
-        <v>175795220</v>
+        <v>29</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="4">
-        <v>62513951</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
@@ -8197,24 +7541,24 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="4">
-        <v>266656979</v>
+        <v>29</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G4" s="4">
-        <v>92504061</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
@@ -8226,24 +7570,24 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F5" s="4">
+        <v>29454534</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>12506101</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
@@ -8255,24 +7599,24 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F6" s="4">
+        <v>25694256</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>10273352</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
@@ -8284,24 +7628,24 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F7" s="4">
+        <v>16153848</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>7366643</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
@@ -8313,24 +7657,24 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F8" s="4">
+        <v>31335623</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>11085612</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
@@ -8342,24 +7686,24 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F9" s="4">
+        <v>16675419</v>
       </c>
       <c r="G9" s="4">
-        <v>0</v>
+        <v>6452607</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>10</v>
@@ -8371,24 +7715,24 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F10" s="4">
+        <v>10469797</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>3799676</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>10</v>
@@ -8400,24 +7744,24 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F11" s="4">
+        <v>15853148</v>
       </c>
       <c r="G11" s="4">
-        <v>0</v>
+        <v>5993537</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>10</v>
@@ -8429,20 +7773,31 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>13</v>
+        <v>29</v>
+      </c>
+      <c r="F12" s="4">
+        <v>32027258</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>10809595</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>36</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8457,15 +7812,15 @@
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -8511,19 +7866,19 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="4">
-        <v>101509937</v>
+        <v>27</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G2" s="4">
-        <v>29542529</v>
+        <v>0</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -8540,19 +7895,19 @@
         <v>11</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="4">
-        <v>175795220</v>
+        <v>27</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="4">
-        <v>62513951</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -8569,19 +7924,19 @@
         <v>11</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="4">
-        <v>266656979</v>
+        <v>27</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G4" s="4">
-        <v>92504061</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -8598,19 +7953,19 @@
         <v>11</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="F5" s="4">
+        <v>324202743</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>128612210</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -8627,19 +7982,19 @@
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="F6" s="4">
+        <v>406524579</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>147504720</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -8656,19 +8011,19 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="F7" s="4">
+        <v>411837802</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>144924295</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -8685,19 +8040,19 @@
         <v>11</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="F8" s="4">
+        <v>654459936</v>
       </c>
       <c r="G8" s="4">
-        <v>0</v>
+        <v>216055261</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
@@ -8714,19 +8069,19 @@
         <v>11</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="F9" s="4">
+        <v>696051137</v>
       </c>
       <c r="G9" s="4">
-        <v>0</v>
+        <v>227900588</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -8743,19 +8098,19 @@
         <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="F10" s="4">
+        <v>692086017</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>235108168</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
@@ -8772,19 +8127,19 @@
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="F11" s="4">
+        <v>810613918</v>
       </c>
       <c r="G11" s="4">
-        <v>0</v>
+        <v>270508386</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
@@ -8801,49 +8156,31 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1241438021</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>366178646</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4">
-        <v>2025</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
